--- a/Questions - Round 11.xlsx
+++ b/Questions - Round 11.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://innochemnv-my.sharepoint.com/personal/zander_fias_innochem_be/Documents/OneDrive_1_25-9-2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stockmeier.sharepoint.com/sites/YoungProfessionalsSTOCKMEIER-YPIII-SustainabilityAwarenessSessions/Freigegebene Dokumente/02. Content/Questions in template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="11_952E35C0F31FD2A9666BB3B0EE9794DDFDF17E23" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A021948E-EB95-4787-A94D-725C64DBE88E}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="11_952E35C0F31FD2A9666BB3B0EE9794DDFDF17E23" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{742BAD6E-982C-4854-BED8-42B95FCD1C61}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="456">
   <si>
     <t>type</t>
   </si>
@@ -1382,6 +1382,18 @@
   </si>
   <si>
     <t>Uczciwe zasady i przejrzyste zgłaszanie problemów budują zaufanie. Osobiste nawyki są ważne, ponieważ wiele drobnych wyborów nabiera znaczenia, gdy powtarza je wiele osób.</t>
+  </si>
+  <si>
+    <t>SDG 16 ersetzen durch Frieden &amp; Gerechtigkeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schere Frage weiß jeder was Zero in Focous ist ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lieferketten ? </t>
+  </si>
+  <si>
+    <t>Schwer, was ist das Hinweisßgebersystem ?</t>
   </si>
 </sst>
 </file>
@@ -1459,7 +1471,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="42">
     <dxf>
@@ -1601,10 +1613,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Questions" displayName="Questions" ref="A1:J11">
   <autoFilter ref="A1:J11" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
@@ -1705,14 +1713,14 @@
   <autoFilter ref="A1:J11" xr:uid="{730858E6-69BC-47C6-86A6-60747033D283}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{F6E0CC1C-5BF8-4344-8753-F4F90DC99ADE}" name="type"/>
-    <tableColumn id="2" xr3:uid="{683F3AD4-28E2-4B49-8679-085E172BF645}" name="question" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{EED24DA3-EA84-4523-975C-401C2E34D3E1}" name="note" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{C8CA43EE-C464-4926-8DCE-EF39B0A1168A}" name="option1" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{6B4AD262-E8A9-4C76-B10B-C13D78C34997}" name="option2" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{AC795E80-E82E-484F-ADE9-A22AB527A0E7}" name="option3" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{B5CF9105-D6DC-403E-944B-78A104A95840}" name="option4" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{683F3AD4-28E2-4B49-8679-085E172BF645}" name="question" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{EED24DA3-EA84-4523-975C-401C2E34D3E1}" name="note" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{C8CA43EE-C464-4926-8DCE-EF39B0A1168A}" name="option1" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{6B4AD262-E8A9-4C76-B10B-C13D78C34997}" name="option2" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{AC795E80-E82E-484F-ADE9-A22AB527A0E7}" name="option3" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{B5CF9105-D6DC-403E-944B-78A104A95840}" name="option4" dataDxfId="8"/>
     <tableColumn id="8" xr3:uid="{601FC185-52AD-4BD1-A6E7-538C8F333107}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{77AF46DB-69A4-4195-AFED-AB0D830FAB19}" name="explanation" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{77AF46DB-69A4-4195-AFED-AB0D830FAB19}" name="explanation" dataDxfId="7"/>
     <tableColumn id="10" xr3:uid="{35AA5CAE-7738-4FFF-88AA-61572668D706}" name="Comments ZF"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1724,14 +1732,14 @@
   <autoFilter ref="A1:J11" xr:uid="{6F524771-F03D-4E22-A2F1-9BE9B1F81F66}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{FDF49872-A62C-494A-B1D2-B9FFD9EE2F59}" name="type"/>
-    <tableColumn id="2" xr3:uid="{1AC86FC0-BFF7-442E-9B83-63D03E0C6E50}" name="question" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{7FE4F10C-7972-4A63-B3BC-DAD4CD7CD2F3}" name="note" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{696EBBDD-456C-4946-8723-ED4BB707F1F3}" name="option1" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{6B4F65BC-944E-4607-BA14-8A636A2B4344}" name="option2" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{C28316DE-E0FB-4268-95BC-BAA01FE19A03}" name="option3" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{8FE7C5C6-0CE1-447E-818D-E30D56AC8AA1}" name="option4" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{1AC86FC0-BFF7-442E-9B83-63D03E0C6E50}" name="question" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{7FE4F10C-7972-4A63-B3BC-DAD4CD7CD2F3}" name="note" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{696EBBDD-456C-4946-8723-ED4BB707F1F3}" name="option1" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{6B4F65BC-944E-4607-BA14-8A636A2B4344}" name="option2" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{C28316DE-E0FB-4268-95BC-BAA01FE19A03}" name="option3" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{8FE7C5C6-0CE1-447E-818D-E30D56AC8AA1}" name="option4" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{3DD82A10-A483-4D9E-A4F4-AC5C558330C0}" name="correct"/>
-    <tableColumn id="9" xr3:uid="{DBC8B9CF-CFAE-4E1C-B1D3-D94FCBD874A2}" name="explanation" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{DBC8B9CF-CFAE-4E1C-B1D3-D94FCBD874A2}" name="explanation" dataDxfId="0"/>
     <tableColumn id="10" xr3:uid="{36611E01-A6DC-406B-9C3A-6DF3FB575A66}" name="Comments ZF"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2024,7 +2032,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -2035,7 +2043,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2067,7 +2075,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2097,7 +2105,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2127,7 +2135,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2157,7 +2165,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2187,7 +2195,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2217,7 +2225,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2247,7 +2255,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2277,7 +2285,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2307,7 +2315,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2337,7 +2345,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2378,7 +2386,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB405279-4715-4A28-AA00-F9FC6E6C7467}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -2389,7 +2397,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2421,7 +2429,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2451,7 +2459,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2481,7 +2489,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2511,7 +2519,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2541,7 +2549,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2571,7 +2579,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2601,7 +2609,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2631,7 +2639,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2661,7 +2669,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2691,7 +2699,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2732,7 +2740,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B468BB66-61DB-41F4-A3E6-6E18BD15C2C8}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -2743,7 +2751,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2775,7 +2783,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2805,7 +2813,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2835,7 +2843,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2865,7 +2873,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2895,7 +2903,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2925,7 +2933,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2955,7 +2963,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2985,7 +2993,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3015,7 +3023,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3045,7 +3053,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3086,7 +3094,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1983B159-4D16-41A2-94A1-E6F3D3B8637B}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -3097,7 +3105,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3129,7 +3137,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -3159,7 +3167,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3187,9 +3195,11 @@
       <c r="I3" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="J3" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3217,9 +3227,11 @@
       <c r="I4" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="J4" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3249,7 +3261,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3279,7 +3291,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3307,9 +3319,11 @@
       <c r="I7" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="J7" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3337,9 +3351,11 @@
       <c r="I8" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="J8" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3367,9 +3383,11 @@
       <c r="I9" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="J9" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3397,9 +3415,11 @@
       <c r="I10" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="J10" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3440,7 +3460,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B100B5D5-03B9-4C8B-8DFE-F46CE262EF43}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -3451,7 +3471,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3483,7 +3503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -3513,7 +3533,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3543,7 +3563,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3573,7 +3593,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3603,7 +3623,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3633,7 +3653,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3663,7 +3683,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3693,7 +3713,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3723,7 +3743,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3753,7 +3773,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3794,7 +3814,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6D6CC87-5C15-4447-AFFF-2592E0DC1D54}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -3805,7 +3825,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3837,7 +3857,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -3867,7 +3887,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3897,7 +3917,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3927,7 +3947,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3957,7 +3977,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3987,7 +4007,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -4017,7 +4037,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -4047,7 +4067,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -4077,7 +4097,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -4107,7 +4127,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -4148,7 +4168,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E7BAA9-CA84-4132-9E36-9397DCCF06B4}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -4159,7 +4179,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4191,7 +4211,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -4221,7 +4241,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -4251,7 +4271,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -4281,7 +4301,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -4311,7 +4331,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -4341,7 +4361,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -4371,7 +4391,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -4401,7 +4421,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -4431,7 +4451,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -4461,7 +4481,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -4510,15 +4530,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006B71C29808C7F3499BFFC3671560B6FA" ma:contentTypeVersion="8" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e4f9e1976b194f932bebfa03c600f49f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2aad7df3-4ab7-4daa-980d-cf7206357ce9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d33a1b74cd678b812bcd025038ca576" ns2:_="">
     <xsd:import namespace="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
@@ -4682,38 +4693,39 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E33CB20E-8CD9-45DC-A017-643021875360}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24AB366B-AF5D-44BF-93FA-453F0A428C19}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1235AC26-E845-47DF-8D09-71C5FA1769EC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{286F70A0-A5F6-4341-B458-53E45BBA0F5C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>